--- a/www/download/IND.emp.s.un.EXI382.xlsx
+++ b/www/download/IND.emp.s.un.EXI382.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10.572</t>
+          <t>10572269.327008</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.763</t>
+          <t>7763499.99999979</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.323</t>
+          <t>8322899.99999864</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>8390300.00000069</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.571</t>
+          <t>8571100.00000246</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>8719599.99999941</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8.948</t>
+          <t>8948100.00000111</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.081</t>
+          <t>9081099.99999795</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9.245</t>
+          <t>9245499.99999836</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9.465</t>
+          <t>9465100.00000224</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>9.623</t>
+          <t>9623299.99999809</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>9.969</t>
+          <t>9968500.00000006</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>10.218</t>
+          <t>10218300.0000003</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>10.512</t>
+          <t>10512199.9999984</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>10740300.0000016</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.921</t>
+          <t>10920599.9999999</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>11.215</t>
+          <t>11214600.0000012</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11.395</t>
+          <t>11394600.0000016</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>11.546</t>
+          <t>11545599.9999998</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.416</t>
+          <t>10416107.6928504</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>9.643</t>
+          <t>9643323.05075511</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>9.819</t>
+          <t>9818890.97615731</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>9.987</t>
+          <t>9986568.22250249</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.297</t>
+          <t>10296647.4071664</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>9.799</t>
+          <t>9798823.85416946</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>9.614</t>
+          <t>9613993.49758796</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>9.634</t>
+          <t>9634264.98219542</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.836</t>
+          <t>4836284.24360325</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.316</t>
+          <t>3316049.99999957</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.099</t>
+          <t>3099079.99999961</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.552</t>
+          <t>3552050.00000005</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.649</t>
+          <t>3648760.00000057</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3689770.00000155</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>3525480</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.581</t>
+          <t>3581060.00000038</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3779940.00000104</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.605</t>
+          <t>3604559.99999996</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3.828</t>
+          <t>3828329.99999929</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.874</t>
+          <t>3873819.99999988</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3.941</t>
+          <t>3941429.99999902</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.919</t>
+          <t>3919370.00000059</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4060189.99999946</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>4.073</t>
+          <t>4072620.00000022</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>4110589.99999996</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4179559.99999935</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>4.203</t>
+          <t>4202989.99999931</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>4.187</t>
+          <t>4186685.83981957</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.226</t>
+          <t>4225656.93377473</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>4336106.9162137</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4.494</t>
+          <t>4494168.87368187</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.672</t>
+          <t>4671852.58894711</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.898</t>
+          <t>4898240.86077417</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>4.899</t>
+          <t>4898520.8068556</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4.896</t>
+          <t>4896247.64439402</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.891</t>
+          <t>4891294.05411481</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.791</t>
+          <t>3790799.9999987</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.801</t>
+          <t>3800700.0000002</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3909599.99999952</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.894</t>
+          <t>3894300.00000092</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.033</t>
+          <t>4033100.00000071</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.114</t>
+          <t>4113700.00000012</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4170400.00000033</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4.162</t>
+          <t>4162200.00000003</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4160200.00000143</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4200199.99999957</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4260199.99999871</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>4.307</t>
+          <t>4307099.99999883</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>4.379</t>
+          <t>4378599.99999992</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4.458</t>
+          <t>4457899.99999987</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>4.449</t>
+          <t>4448900.00000057</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>4.479</t>
+          <t>4479000.0000005</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>4.518</t>
+          <t>4518099.99999895</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>4.556</t>
+          <t>4555699.99999948</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>4.542</t>
+          <t>4542382.56943422</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.449</t>
+          <t>4449212.88307794</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>4.563</t>
+          <t>4563292.02606301</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>4.624</t>
+          <t>4623690.33884952</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4739592.31151726</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.818</t>
+          <t>4818039.02449383</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>4.855</t>
+          <t>4855112.80260933</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>4.834</t>
+          <t>4833924.86119354</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.876</t>
+          <t>4875867.61583906</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3119799.99999941</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3040400.00000034</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.894</t>
+          <t>2894100.00000083</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.757</t>
+          <t>2757000.00000012</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.819</t>
+          <t>2819499.9999994</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.597</t>
+          <t>2597399.99999963</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.716</t>
+          <t>2715900.00000045</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.714</t>
+          <t>2714499.99999933</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.894</t>
+          <t>2894200.00000061</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2959500.00000039</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.011</t>
+          <t>3010999.99999905</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3.122</t>
+          <t>3121900.00000044</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.236</t>
+          <t>3235900.00000019</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.353</t>
+          <t>3353099.99999957</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>3.209</t>
+          <t>3209200.00000063</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>3.044</t>
+          <t>3044200.00000018</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.958</t>
+          <t>2958299.99999917</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.927</t>
+          <t>2926999.99999984</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.786</t>
+          <t>2786219.13357632</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.972</t>
+          <t>2972368.54141268</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3.133</t>
+          <t>3132696.55914527</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3229636.57630341</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.486</t>
+          <t>3485716.1167078</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.809</t>
+          <t>3809394.4733136</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>4.114</t>
+          <t>4114302.60511159</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>4.327</t>
+          <t>4326993.81085294</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>84.621</t>
+          <t>84620818.4870092</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>72.216</t>
+          <t>72216300.0000008</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>70.414</t>
+          <t>70414499.9999894</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.761</t>
+          <t>71760700.0000021</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>72.347</t>
+          <t>72346599.9999958</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>74.08</t>
+          <t>74079500.0000084</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>75.019</t>
+          <t>75019300.0000121</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.655</t>
+          <t>77654700.000019</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>78.752</t>
+          <t>78752100.000012</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>79.961</t>
+          <t>79960799.9999954</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>84.365</t>
+          <t>84364699.9999769</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>86.982</t>
+          <t>86981599.9999919</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>89.098</t>
+          <t>89098000.0000177</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>90.573</t>
+          <t>90573299.9999803</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>91.528</t>
+          <t>91527800.000005</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>92.483</t>
+          <t>92483000.0000136</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>92.921</t>
+          <t>92920949.999975</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>93.359</t>
+          <t>93359199.9999787</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>94.637</t>
+          <t>94636800.0000015</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>91.576</t>
+          <t>91576060.4107947</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>90.025</t>
+          <t>90025036.4233644</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>75.659</t>
+          <t>75659478.8600962</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>76.626</t>
+          <t>76625638.8260328</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>85.471</t>
+          <t>85471326.2963758</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>76.646</t>
+          <t>76646252.8216248</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>78.776</t>
+          <t>78775553.0997118</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>76.472</t>
+          <t>76471657.1245312</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14.022</t>
+          <t>14022349.3779251</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.292</t>
+          <t>13291989.9999975</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12.019</t>
+          <t>12018530.0000023</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.699</t>
+          <t>12699475.0000001</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12.976</t>
+          <t>12976394.9999993</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14.741</t>
+          <t>14740914.999999</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15.086</t>
+          <t>15085524.9999997</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.176</t>
+          <t>15176109.9999986</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15.609</t>
+          <t>15608920.0000022</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15.942</t>
+          <t>15942019.9999963</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16.208</t>
+          <t>16208254.9999998</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>14.902</t>
+          <t>14902050.000001</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>16.725</t>
+          <t>16725350.0000003</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>17.099</t>
+          <t>17098950.0000034</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>17.378</t>
+          <t>17377510.0000008</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>15.837</t>
+          <t>15836849.9999966</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>17.385</t>
+          <t>17384844.9999981</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>17.683</t>
+          <t>17682525.0000013</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>17.851</t>
+          <t>17850790.0000013</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>16.651</t>
+          <t>16651196.5604181</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>15.496</t>
+          <t>15495651.6994046</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>15.501</t>
+          <t>15501071.4582232</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>14.858</t>
+          <t>14858455.5199325</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.897</t>
+          <t>14896779.5405197</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>14.306</t>
+          <t>14306338.9267869</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14.983</t>
+          <t>14982579.7974967</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>14.557</t>
+          <t>14557464.1209483</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1414.195</t>
+          <t>1414195461.49155</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>563.524</t>
+          <t>563523500.00002</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>571.43</t>
+          <t>571429900.000141</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>576.251</t>
+          <t>576250600.000092</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>560.604</t>
+          <t>560603700.000012</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>563.269</t>
+          <t>563268599.999922</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>561.639</t>
+          <t>561639099.999931</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>559.975</t>
+          <t>559974799.999981</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>562.223</t>
+          <t>562223499.999949</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>554.292</t>
+          <t>554292100.00017</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>557.997</t>
+          <t>557997299.999877</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>571.855</t>
+          <t>571854600.000057</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>588.672</t>
+          <t>588671799.999998</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>602.132</t>
+          <t>602132200.000007</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>586.445</t>
+          <t>586445200.000028</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>565.957</t>
+          <t>565957400.00002</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>600.768</t>
+          <t>600768100.000136</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>627.379</t>
+          <t>627379499.999993</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>635.611</t>
+          <t>635610599.999885</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>667.071</t>
+          <t>667070706.51213</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>718.124</t>
+          <t>718123940.62448</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>873.528</t>
+          <t>873528486.421284</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>864.527</t>
+          <t>864526758.833289</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>932.682</t>
+          <t>932682022.345919</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>974.65</t>
+          <t>974650373.90545</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>1074.382</t>
+          <t>1074381533.21317</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1130.075</t>
+          <t>1130074925.94114</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>506440.336175415</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>263899.999999981</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>268074.999999902</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272550.000000061</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>276925.000000047</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>278600.000000022</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>291499.99999999</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>305900.00000008</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>316200.000000024</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>326399.999999976</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337299.999999954</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>348900.000000008</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356699.999999937</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377699.999999988</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>390099.999999914</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>389700.000000006</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>401700.000000015</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>399300.000000019</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>391699.999999917</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>361522.949056271</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>361978.819010386</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>380003.190204543</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>428242.727527128</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>440219.826636322</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>472455.857385203</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>494920.980608346</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>509398.297919137</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6740102.00638638</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5010393.00000001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4.908</t>
+          <t>4908077.00000167</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5.096</t>
+          <t>5095984.99999932</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5079955.99999947</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4899701.99999925</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.859</t>
+          <t>4859341.00000045</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.757</t>
+          <t>4757043.00000097</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.873</t>
+          <t>4873144.00000007</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4.748</t>
+          <t>4747863.99999921</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4.829</t>
+          <t>4828885.99999987</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4.923</t>
+          <t>4922640.00000187</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4.989</t>
+          <t>4988977.00000021</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>5.093</t>
+          <t>5093142.9999987</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>5.204</t>
+          <t>5204079.00000009</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5110099.9999994</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>5.057</t>
+          <t>5057241.00000058</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4.918</t>
+          <t>4917662.0000005</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>5.065</t>
+          <t>5064632.00000011</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>4.752</t>
+          <t>4751657.11105563</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>4.594</t>
+          <t>4593512.28767099</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>4.859</t>
+          <t>4859442.31073983</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>4.944</t>
+          <t>4943673.1998203</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.262</t>
+          <t>5262219.92745028</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>5.686</t>
+          <t>5685678.99154646</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>6.035</t>
+          <t>6035032.52176854</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>6.127</t>
+          <t>6127047.59697606</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>51.285</t>
+          <t>51285055.9535133</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.958</t>
+          <t>37958000.0000038</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37.969</t>
+          <t>37968999.9999987</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.947</t>
+          <t>37947000.0000004</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>38.407</t>
+          <t>38406999.9999913</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>39.031</t>
+          <t>39030999.9999851</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>39.917</t>
+          <t>39916999.9999916</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>39.809</t>
+          <t>39809000.000014</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>39629999.9999945</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39200000.0000103</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>38.898</t>
+          <t>38898000.0000094</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>39.326</t>
+          <t>39325999.9999935</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>39.635</t>
+          <t>39634999.9999943</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>40.325</t>
+          <t>40325000.0000013</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>40.856</t>
+          <t>40855999.9999853</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>40.892</t>
+          <t>40892000.0000089</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>41019999.9999955</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41570000.0000004</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>42.033</t>
+          <t>42033000.0000005</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>42.771</t>
+          <t>42770891.2336743</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>44.554</t>
+          <t>44554000.1207533</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>44.286</t>
+          <t>44285904.7380612</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>44.993</t>
+          <t>44992761.6903577</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>48.032</t>
+          <t>48031562.6912767</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>46.997</t>
+          <t>46996985.7912794</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>47.887</t>
+          <t>47886952.0183142</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>49.945</t>
+          <t>49944713.0960498</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.648</t>
+          <t>2648184.37603511</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.715</t>
+          <t>2714700.00000031</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.739</t>
+          <t>2738899.99999986</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2.588</t>
+          <t>2588299.99999929</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2339900.00000004</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.813</t>
+          <t>2813300.00000019</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.814</t>
+          <t>2814499.99999949</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.827</t>
+          <t>2826500.00000022</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.845</t>
+          <t>2844800.00000057</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2809899.99999908</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2.856</t>
+          <t>2855599.99999988</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.695</t>
+          <t>2695400.0000008</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2.915</t>
+          <t>2915300.00000006</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.913</t>
+          <t>2912700.00000002</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.848</t>
+          <t>2847900.00000044</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2.732</t>
+          <t>2732400.00000062</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2.703</t>
+          <t>2703100.00000014</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.698</t>
+          <t>2698200.00000064</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2.684</t>
+          <t>2683500.00000017</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2.746</t>
+          <t>2745869.68468992</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.891</t>
+          <t>2891224.22446814</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2.792</t>
+          <t>2791876.41976038</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2.789</t>
+          <t>2788890.40017992</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.791</t>
+          <t>2790911.73290675</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.569</t>
+          <t>2569307.64360747</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2.533</t>
+          <t>2533109.71220414</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2540181.51885677</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19.208</t>
+          <t>19208395.0476339</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.827</t>
+          <t>12827299.9999993</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13.131</t>
+          <t>13131399.9999986</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13.612</t>
+          <t>13611600.0000012</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14.158</t>
+          <t>14158099.9999993</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.004</t>
+          <t>15004400.0000046</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15.848</t>
+          <t>15847599.9999982</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.497</t>
+          <t>16497000.0000043</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17200100.000001</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.869</t>
+          <t>17869100.0000029</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>18.483</t>
+          <t>18483399.9999964</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>19.693</t>
+          <t>19692500.0000012</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>20.445</t>
+          <t>20445200.0000011</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>21.093</t>
+          <t>21092899.9999964</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.468</t>
+          <t>20467699.9999963</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>19.105</t>
+          <t>19104799.999998</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>18.722</t>
+          <t>18721900.0000014</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>18.417</t>
+          <t>18417099.9999967</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>17.627</t>
+          <t>17627400.0000012</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16990177.5094222</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>16.869</t>
+          <t>16868969.2899003</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>17.661</t>
+          <t>17661174.7086437</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>17.922</t>
+          <t>17922451.2702864</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18.099</t>
+          <t>18099199.4715752</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18560476.1909361</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18.527</t>
+          <t>18527114.666854</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>18.957</t>
+          <t>18956984.8343973</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.312</t>
+          <t>1311694.16747338</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>642499.999999938</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>615499.999999996</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>609900.00000001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>616399.999999925</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>557499.999999977</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>594599.999999903</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>590300.000000069</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>596299.999999995</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>603700.000000114</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>609500.000000063</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>622100.000000003</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>659299.999999969</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>664499.99999996</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>654599.999999997</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>593000.000000048</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>567100.000000046</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>602600.000000155</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>614100.000000125</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>639181.167940485</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>614157.258559257</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>635775.449525789</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>674556.63098712</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>690723.7600857</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>762735.713549925</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>826202.888610295</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.843</t>
+          <t>843402.870687734</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.378</t>
+          <t>2378156.83269949</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2090300.00000019</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>2116399.99999964</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.197</t>
+          <t>2197200.00000018</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.269</t>
+          <t>2269300</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.413</t>
+          <t>2412699.99999986</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>2451000.00000067</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.489</t>
+          <t>2488799.99999972</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.488</t>
+          <t>2488299.99999971</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.478</t>
+          <t>2478299.9999998</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.461</t>
+          <t>2460699.99999963</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.481</t>
+          <t>2480500.00000022</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>2523300.00000051</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.571</t>
+          <t>2570600.00000041</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.353</t>
+          <t>2352800.00000089</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2.447</t>
+          <t>2447200.00000072</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>2434999.99999934</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.463</t>
+          <t>2462500.00000034</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2.471</t>
+          <t>2471300.00000021</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.388</t>
+          <t>2388283.29821005</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.404</t>
+          <t>2404311.89423249</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2.406</t>
+          <t>2405847.18827674</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2.422</t>
+          <t>2422113.77913696</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.423</t>
+          <t>2422558.3201327</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.558</t>
+          <t>2558133.7498214</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2.447</t>
+          <t>2446515.00069052</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>2473261.50307585</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>24.236</t>
+          <t>24235952.4096585</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21.266</t>
+          <t>21265999.9999984</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23.823</t>
+          <t>23822999.9999939</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24.012</t>
+          <t>24011999.9999973</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19.624</t>
+          <t>19624000.000006</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25.033</t>
+          <t>25032999.9999994</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25.672</t>
+          <t>25672000.0000007</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26.041</t>
+          <t>26041000.0000009</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>26.161</t>
+          <t>26160999.9999987</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>26.164</t>
+          <t>26164000.000011</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>26.192</t>
+          <t>26191999.9999965</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>26.376</t>
+          <t>26376000.0000023</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>26.667</t>
+          <t>26666999.9999927</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>27.042</t>
+          <t>27041999.9999922</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>27.167</t>
+          <t>27166999.9999991</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>26.858</t>
+          <t>26858000.0000002</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>26.875</t>
+          <t>26875000.0000033</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>27.061</t>
+          <t>27061000.0000034</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>27.096</t>
+          <t>27096000.0000038</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>25.944</t>
+          <t>25943877.953166</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>26.057</t>
+          <t>26056930.3138178</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26019662.6298758</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>25.535</t>
+          <t>25535110.4987111</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>24.455</t>
+          <t>24454971.7970351</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>25.248</t>
+          <t>25247542.3001975</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>25.218</t>
+          <t>25217572.2820281</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>24.949</t>
+          <t>24948699.5689197</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>35.429</t>
+          <t>35428802.6573851</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26.461</t>
+          <t>26460899.9999992</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27.202</t>
+          <t>27202399.9999995</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>27.729</t>
+          <t>27728700.0000013</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28.076</t>
+          <t>28076300.0000035</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>27.912</t>
+          <t>27912199.9999991</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28.361</t>
+          <t>28361200.000004</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>27.369</t>
+          <t>27368799.9999928</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>28.893</t>
+          <t>28893499.9999954</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>29.182</t>
+          <t>29181900.0000053</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>29.394</t>
+          <t>29394300.0000065</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>29.816</t>
+          <t>29816000.0000098</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>30.071</t>
+          <t>30071300.0000035</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>30.264</t>
+          <t>30263599.9999966</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>29.253</t>
+          <t>29253299.9999982</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>28.687</t>
+          <t>28687499.9999978</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>28.691</t>
+          <t>28690699.9999955</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>28.819</t>
+          <t>28818999.9999968</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>29.101</t>
+          <t>29100799.9999908</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>28.907</t>
+          <t>28906695.5660623</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>31.543</t>
+          <t>31543347.3056017</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>36.371</t>
+          <t>36370940.6645325</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>32.381</t>
+          <t>32381497.0191983</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>31.349</t>
+          <t>31349451.4485172</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>32.839</t>
+          <t>32838913.3859083</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>34.304</t>
+          <t>34304075.4118459</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>34.621</t>
+          <t>34621086.3560279</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.568</t>
+          <t>3567685.32554459</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.877</t>
+          <t>3876800.00000067</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.925</t>
+          <t>3924900.00000048</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3909599.99999969</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4.072</t>
+          <t>4071999.99999961</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.099</t>
+          <t>4098500.0000002</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4149700.00000019</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4.157</t>
+          <t>4156600.00000145</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.238</t>
+          <t>4237599.99999973</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4.341</t>
+          <t>4341200.00000044</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4.385</t>
+          <t>4385400.00000127</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.424</t>
+          <t>4423799.99999958</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4510400.00000011</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4.567</t>
+          <t>4567400.00000018</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4.558</t>
+          <t>4557999.99999988</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>4.489</t>
+          <t>4488600.00000067</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>4.387</t>
+          <t>4387299.99999905</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4.089</t>
+          <t>4088699.99999931</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>3.761</t>
+          <t>3761299.99999963</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3519775.77139323</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.315</t>
+          <t>3314704.90651156</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>3.301</t>
+          <t>3300957.78614726</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>3.133</t>
+          <t>3133472.06408364</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.264</t>
+          <t>3264486.38132961</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.277</t>
+          <t>3277437.12425377</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>3.343</t>
+          <t>3342557.50672917</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>3.373</t>
+          <t>3372708.76230504</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.667</t>
+          <t>4667359.02584707</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.801</t>
+          <t>3800599.99999927</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.703</t>
+          <t>3702700.00000049</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.661</t>
+          <t>3661000.0000011</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.726</t>
+          <t>3725900.00000105</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.855</t>
+          <t>3855100.00000025</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.813</t>
+          <t>3812899.99999977</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.963</t>
+          <t>3963399.99999917</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.792</t>
+          <t>3792300.00000031</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.028</t>
+          <t>4028300.00000065</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.993</t>
+          <t>3993199.99999893</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.924</t>
+          <t>3923799.99999997</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.033</t>
+          <t>4033099.99999975</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.027</t>
+          <t>4026700.00000031</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.809</t>
+          <t>3809300.00000139</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.782</t>
+          <t>3781999.99999995</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3780299.999999</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3810199.99999885</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>3875699.99999992</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.795</t>
+          <t>3795386.19702844</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>3.804</t>
+          <t>3804237.05474518</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>4.023</t>
+          <t>4023310.28628319</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>3.982</t>
+          <t>3982274.1408267</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4.298</t>
+          <t>4298340.20077619</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>4.599</t>
+          <t>4599346.30792883</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4770028.4868884</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4.887</t>
+          <t>4886626.59911943</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>903.992</t>
+          <t>903992381.652153</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>343.831</t>
+          <t>343830700.000025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>347.06</t>
+          <t>347060100.000062</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>350.402</t>
+          <t>350401800.000031</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>340.596</t>
+          <t>340595800.00023</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>354.792</t>
+          <t>354792199.999978</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>368.966</t>
+          <t>368966000.000008</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>371.303</t>
+          <t>371303199.999934</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>368.071</t>
+          <t>368070799.999929</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>369.935</t>
+          <t>369935200.000009</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>366.99</t>
+          <t>366990499.999771</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>371.99</t>
+          <t>371989599.999891</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>372.913</t>
+          <t>372912799.999946</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>373.531</t>
+          <t>373531200.000065</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>373.848</t>
+          <t>373847800.000054</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>374.535</t>
+          <t>374535000.000104</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>374.286</t>
+          <t>374285600.000025</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>377.183</t>
+          <t>377183100.000033</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>379.204</t>
+          <t>379204100.000013</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>373.496</t>
+          <t>373496426.913781</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>393.622</t>
+          <t>393621787.498038</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>484.106</t>
+          <t>484106211.169331</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>518.33</t>
+          <t>518329562.339685</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>580.329</t>
+          <t>580328668.407889</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>578.665</t>
+          <t>578665223.625424</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>639.782</t>
+          <t>639781881.582791</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>684.917</t>
+          <t>684916532.718532</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>185.241</t>
+          <t>185240906.763822</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80099900.0000084</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.691</t>
+          <t>85691499.9999908</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>86.944</t>
+          <t>86943600.00001</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>87.672</t>
+          <t>87672099.9999858</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>88.673</t>
+          <t>88672899.9999859</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>85.797</t>
+          <t>85797399.9999813</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>90.799</t>
+          <t>90798900.0000315</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>89.891</t>
+          <t>89890699.9999751</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>91.222</t>
+          <t>91221600.0000023</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>96.95</t>
+          <t>96949699.9999861</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>95.355</t>
+          <t>95355299.999987</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>98.017</t>
+          <t>98016799.9999797</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>98.831</t>
+          <t>98831400.0000127</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>104.641</t>
+          <t>104641299.999987</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>107.069</t>
+          <t>107068600.000009</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>109.588</t>
+          <t>109587900</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>104.269</t>
+          <t>104269400.000007</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>113.01</t>
+          <t>113009799.999992</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>111.079</t>
+          <t>111078885.887917</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>104.771</t>
+          <t>104771020.362046</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>129.917</t>
+          <t>129916986.325096</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>138.068</t>
+          <t>138068201.881693</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>127.868</t>
+          <t>127867912.625199</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>124.245</t>
+          <t>124244786.279616</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>138.278</t>
+          <t>138277831.747675</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>145.559</t>
+          <t>145559338.64777</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.694</t>
+          <t>3694129.38598761</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1190699.99999997</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1285799.99999995</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1362900.00000003</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1412499.99999987</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1576599.99999992</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.656</t>
+          <t>1655900.00000044</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.712</t>
+          <t>1712399.99999954</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.716</t>
+          <t>1716300.00000004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1785400.00000029</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.824</t>
+          <t>1824100.00000033</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1934000.0000003</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>2025300.00000005</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.101</t>
+          <t>2100999.99999959</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2.092</t>
+          <t>2092200.00000006</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1869800.00000067</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1.872</t>
+          <t>1872499.99999957</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.843</t>
+          <t>1842600.00000014</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1.752</t>
+          <t>1752000.00000012</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1884094.40691505</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>1.964</t>
+          <t>1964381.80227348</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2499786.84003979</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2.792</t>
+          <t>2791689.5697236</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2839878.77268885</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2.968</t>
+          <t>2968367.96129211</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>3.271</t>
+          <t>3271098.26157547</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>3.487</t>
+          <t>3487126.519242</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24190081.2401435</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20.585</t>
+          <t>20585400.0000005</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20.706</t>
+          <t>20705600.0000005</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20.809</t>
+          <t>20809099.9999958</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20.973</t>
+          <t>20973499.9999966</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>21.209</t>
+          <t>21209499.999997</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>21.525</t>
+          <t>21525000.0000006</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21.955</t>
+          <t>21955000.0000076</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22.358</t>
+          <t>22357799.9999964</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>22.652</t>
+          <t>22651699.9999964</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>23.021</t>
+          <t>23021000.0000051</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>23.175</t>
+          <t>23175199.9999989</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>23.594</t>
+          <t>23594399.9999922</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>23.799</t>
+          <t>23798800.0000025</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>23.369</t>
+          <t>23368700.0000038</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>23.002</t>
+          <t>23001799.9999995</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>22.859</t>
+          <t>22859399.9999991</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>22.951</t>
+          <t>22951400.0000018</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>22.886</t>
+          <t>22885900.0000066</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>22.199</t>
+          <t>22198815.6988804</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>22.264</t>
+          <t>22264156.6822155</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>22.498</t>
+          <t>22498471.7341877</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22649512.3159225</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>22.987</t>
+          <t>22987006.3226949</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>23.909</t>
+          <t>23908558.3726447</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23.476</t>
+          <t>23476231.6130682</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>23.886</t>
+          <t>23885540.528094</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>48.803</t>
+          <t>48802550.5843445</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>66.915</t>
+          <t>66915100.0000025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67.155</t>
+          <t>67154800.000007</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>67.829</t>
+          <t>67828599.9999928</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>67.333</t>
+          <t>67332999.9999976</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>66.79</t>
+          <t>66790000.0000114</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>66.646</t>
+          <t>66645999.9999969</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>66.219</t>
+          <t>66218999.9999917</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>65.268</t>
+          <t>65267500.0000009</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>65.019</t>
+          <t>65018599.999992</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>65.021</t>
+          <t>65021199.9999911</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>65.235</t>
+          <t>65234800.0000138</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>65.604</t>
+          <t>65604399.999985</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>65.825</t>
+          <t>65824999.9999996</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>65.522</t>
+          <t>65521800.0000025</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63020000.0000026</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>62760000.0000127</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>62.505</t>
+          <t>62505000.0000063</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>62.04</t>
+          <t>62040000.0000029</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>48.161</t>
+          <t>48160536.9017475</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>48.057</t>
+          <t>48056974.9286325</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>49.902</t>
+          <t>49902201.3593543</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>53.002</t>
+          <t>53001868.9156407</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>49.53</t>
+          <t>49530075.6696753</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>48.857</t>
+          <t>48857424.7553704</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51940398.1336536</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>51.548</t>
+          <t>51547876.0974616</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>37.777</t>
+          <t>37777168.9064571</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20470499.9999992</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20.857</t>
+          <t>20857400.0000033</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>21.151</t>
+          <t>21150799.9999972</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>20019799.9999997</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>20.308</t>
+          <t>20307900.0000006</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21.184</t>
+          <t>21183999.9999969</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21.601</t>
+          <t>21600500.0000037</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22.191</t>
+          <t>22190999.9999962</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22.174</t>
+          <t>22174000.0000074</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>22.587</t>
+          <t>22587000.0000039</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>22.885</t>
+          <t>22885199.9999998</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>23.188</t>
+          <t>23188199.9999982</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>23.348</t>
+          <t>23348400.0000014</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>23.679</t>
+          <t>23678699.9999989</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>23.493</t>
+          <t>23493099.9999942</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>23.816</t>
+          <t>23815599.9999985</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>24.232</t>
+          <t>24231599.9999966</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>24.671</t>
+          <t>24671399.9999932</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>23.426</t>
+          <t>23426143.3800846</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>28.325</t>
+          <t>28325408.3365928</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>33.323</t>
+          <t>33322823.0226519</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>33.152</t>
+          <t>33152447.2575494</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>34.129</t>
+          <t>34128999.9682418</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>34.174</t>
+          <t>34174077.3234212</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>34.307</t>
+          <t>34306606.8787629</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>34.274</t>
+          <t>34274098.4086232</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.968</t>
+          <t>1967847.91704524</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1529000.00000005</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1523400.00000012</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1534099.99999973</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.537</t>
+          <t>1536799.99999996</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.539</t>
+          <t>1539000.00000009</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1469799.99999984</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1402400.00000002</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1440700.00000002</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1489399.99999988</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1446999.99999973</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1475199.99999985</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1468999.9999997</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1494700.00000032</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1425499.99999978</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1317300.0000002</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1.248</t>
+          <t>1247599.9999999</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.252</t>
+          <t>1251700.00000038</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>1275899.99999976</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1.298</t>
+          <t>1297535.81776572</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>1332036.57313509</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1368803.0511093</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1403852.44621077</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1523129.47399678</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1.671</t>
+          <t>1670547.86787402</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>1.717</t>
+          <t>1717020.96797843</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>1799057.19071276</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337325.926931636</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>159200.000000026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162499.999999964</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164699.999999938</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162999.999999995</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169300.000000019</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173800.000000063</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182200.000000004</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182300.000000066</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181600.000000049</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>180999.999999954</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186299.999999961</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>192199.999999992</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194800.000000026</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191400.000000053</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>199399.999999981</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>197099.999999994</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>204400.000000003</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>216399.999999997</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226682.59593969</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>259513.946752724</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273694.301769222</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>283918.979690789</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>283827.608869209</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>291704.79985723</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308059.228142981</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>317322.536084126</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1338303.34095889</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1105200.00000002</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.051</t>
+          <t>1051100.00000012</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.034</t>
+          <t>1033900.00000003</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.965</t>
+          <t>964699.999999967</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.016</t>
+          <t>1016100.00000034</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>984200.000000064</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.004</t>
+          <t>1004499.99999986</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1027800.00000001</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1049699.9999998</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1.072</t>
+          <t>1072200.00000003</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1079000.0000003</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1138400.00000018</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1073300.00000006</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1054599.99999991</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>908200.000000136</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>850399.999999986</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>801900.000000093</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>853299.99999988</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>922343.554213044</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>870945.717114222</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>976288.062661292</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>922894.594944522</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>1.051</t>
+          <t>1050849.4514973</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1.112</t>
+          <t>1111608.93157494</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>1097333.32138247</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>1133904.50949482</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>70.817</t>
+          <t>70817196.2364064</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31.719</t>
+          <t>31719399.999993</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33.804</t>
+          <t>33804099.9999971</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>35.787</t>
+          <t>35787499.9999912</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>36.712</t>
+          <t>36711799.9999954</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>37.125</t>
+          <t>37125000.0000127</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>37.891</t>
+          <t>37891400.0000086</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>37930299.9999972</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>38.798</t>
+          <t>38797999.9999952</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>39.085</t>
+          <t>39085300.0000061</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>40.401</t>
+          <t>40400699.9999983</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>40540000.0000002</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>41.885</t>
+          <t>41885400.0000001</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>42.602</t>
+          <t>42601900.0000071</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43529700.0000035</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>44.555</t>
+          <t>44554699.9999954</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>45.579</t>
+          <t>45579100.0000023</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>46.604</t>
+          <t>46603799.9999924</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>48.647</t>
+          <t>48646799.9999921</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>50.842</t>
+          <t>50842479.7716238</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>57.78</t>
+          <t>57779557.2108438</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>55.003</t>
+          <t>55003405.2252661</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>48.969</t>
+          <t>48969258.9575233</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>56060699.8786464</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>57.318</t>
+          <t>57317939.162401</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>62.721</t>
+          <t>62720812.8978882</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>64.147</t>
+          <t>64146697.0370913</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>333287.2161496</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>128620.000000023</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140160.000000009</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>143959.999999985</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>146150.000000004</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148210.000000013</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149499.999999983</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>154600.000000012</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155199.999999998</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156099.999999961</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152499.99999999</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155500.000000003</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152100.000000001</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>161699.999999991</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158400</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>159099.999999984</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162300</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165999.99999999</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169899.999999979</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>186859.470651288</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>211502.225974137</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227420.853399163</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>242201.751411135</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>268413.225783019</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304001.269686604</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>319789.786451518</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>329510.661096461</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8.724</t>
+          <t>8723930.18944044</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6850199.99999987</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6.811</t>
+          <t>6810999.99999821</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7039700.00000098</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7349900.00000046</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>7.496</t>
+          <t>7496399.99999935</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7.651</t>
+          <t>7651499.9999997</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>7.926</t>
+          <t>7925800.00000165</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>7.701</t>
+          <t>7701000.00000196</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8150299.99999959</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>8029899.99999987</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>8.049</t>
+          <t>8048600.0000023</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>8.233</t>
+          <t>8232500.0000006</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>8.462</t>
+          <t>8462400.00000257</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>8.104</t>
+          <t>8104199.99999494</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>7.902</t>
+          <t>7901599.99999976</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>7.567</t>
+          <t>7567399.99999878</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>7469999.99999849</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>7.579</t>
+          <t>7578700.00000176</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>7.322</t>
+          <t>7321952.25812053</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>7.382</t>
+          <t>7381719.34975351</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>7.229</t>
+          <t>7228906.18242069</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>7.218</t>
+          <t>7217540.15696454</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>7.493</t>
+          <t>7492958.59562004</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7549830.45929237</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>7.619</t>
+          <t>7619100.91444626</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>7.635</t>
+          <t>7634726.30178993</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20.244</t>
+          <t>20243600.6273502</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15.212</t>
+          <t>15212399.999999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15.417</t>
+          <t>15417099.9999989</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15.301</t>
+          <t>15301200.0000001</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15.185</t>
+          <t>15185000.000003</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14.867</t>
+          <t>14866700.0000025</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14.953</t>
+          <t>14952999.9999981</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>14.694</t>
+          <t>14693900.0000001</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>14.237</t>
+          <t>14236800.0000005</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>14.058</t>
+          <t>14057600</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>14.068</t>
+          <t>14068299.9999971</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>14.508</t>
+          <t>14508200.0000011</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>14.999</t>
+          <t>14999499.9999946</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>15.648</t>
+          <t>15648199.9999975</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>15.792</t>
+          <t>15791800.0000043</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>15.859</t>
+          <t>15858699.9999987</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>15.461</t>
+          <t>15461399.9999988</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>15.556</t>
+          <t>15556100.0000029</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>15.583</t>
+          <t>15582700.0000005</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>15.458</t>
+          <t>15458203.910241</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>15.515</t>
+          <t>15515407.9023472</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>15.915</t>
+          <t>15915292.0149966</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>15.439</t>
+          <t>15439413.0065393</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16.991</t>
+          <t>16991206.5658971</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17120166.4516004</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18.272</t>
+          <t>18271973.3034223</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>18.933</t>
+          <t>18933136.8784118</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5.371</t>
+          <t>5371342.74742336</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.481</t>
+          <t>4481200.00000036</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4490100.00000149</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4.585</t>
+          <t>4585000.00000001</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4.927</t>
+          <t>4927100.00000052</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.963</t>
+          <t>4962599.99999948</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5.059</t>
+          <t>5058599.99999839</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5.166</t>
+          <t>5165999.99999981</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5.227</t>
+          <t>5226699.99999996</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5.185</t>
+          <t>5185300.00000038</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5.189</t>
+          <t>5189200.00000077</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>5.184</t>
+          <t>5184299.99999979</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>5.225</t>
+          <t>5225399.99999832</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>5.237</t>
+          <t>5237499.99999931</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>5.196</t>
+          <t>5195500.00000009</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>5.052</t>
+          <t>5051599.99999886</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>4.974</t>
+          <t>4974199.99999859</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>4.835</t>
+          <t>4835199.99999908</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>4.633</t>
+          <t>4632500.00000118</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4610433.85975205</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>4.596</t>
+          <t>4595730.38623309</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>4.661</t>
+          <t>4660697.22069932</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>4.733</t>
+          <t>4732598.93852542</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>5.016</t>
+          <t>5015978.53097347</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5150020.65612343</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>5.232</t>
+          <t>5231673.08980152</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>5.293</t>
+          <t>5292700.99283354</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>15.083</t>
+          <t>15082679.5132547</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10.778</t>
+          <t>10778000.0000009</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>10.256</t>
+          <t>10255999.9999996</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10.881</t>
+          <t>10880899.9999996</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11.106</t>
+          <t>11105600.0000021</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10.994</t>
+          <t>10993599.9999994</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10.865</t>
+          <t>10864799.9999993</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>10.423</t>
+          <t>10422600.0000012</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>9.359</t>
+          <t>9359300.00000028</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8.954</t>
+          <t>8954000.00000134</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>9.225</t>
+          <t>9224700.00000002</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>8.791</t>
+          <t>8790699.99999965</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>9.225</t>
+          <t>9225100.00000072</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>9.283</t>
+          <t>9282699.99999887</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>9.183</t>
+          <t>9182899.99999773</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>9.069</t>
+          <t>9069399.99999934</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>8.564</t>
+          <t>8563899.99999944</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>8440300.0000006</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>8.697</t>
+          <t>8697099.99999987</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>9.811</t>
+          <t>9810968.63605167</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>9.802</t>
+          <t>9801836.33718596</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>10.697</t>
+          <t>10696814.9491547</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>11.107</t>
+          <t>11107338.0207565</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12.999</t>
+          <t>12999084.0528083</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>14.101</t>
+          <t>14101277.9962721</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14.324</t>
+          <t>14324118.8880684</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>14.351</t>
+          <t>14351188.5748453</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>67.494</t>
+          <t>67493592.7169372</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>59.564</t>
+          <t>59563599.9999983</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>59.621</t>
+          <t>59620799.9999952</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>59.122</t>
+          <t>59122199.9999927</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>58.458</t>
+          <t>58457899.9999932</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>62.938</t>
+          <t>62938100.0000046</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>65.068</t>
+          <t>65068100.0000216</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>65.119</t>
+          <t>65118999.9999972</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>66.655</t>
+          <t>66654999.9999995</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>66.426</t>
+          <t>66426099.9999999</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>62.442</t>
+          <t>62441999.999984</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>68.162</t>
+          <t>68161999.9999917</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>68.851</t>
+          <t>68851099.9999974</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>70.556</t>
+          <t>70556099.9999936</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>67.063</t>
+          <t>67062899.9999636</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>69.253</t>
+          <t>69253100.0000023</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>69779800.0000097</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>64.318</t>
+          <t>64318499.9999971</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>71.516</t>
+          <t>71516300.0000139</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>72.949</t>
+          <t>72949109.9928861</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>63.596</t>
+          <t>63595777.8849782</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>51.166</t>
+          <t>51166435.5589747</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>48.122</t>
+          <t>48121681.1346957</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>57.525</t>
+          <t>57525495.2561516</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>57.025</t>
+          <t>57025127.2052509</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>61.474</t>
+          <t>61474355.4484334</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>62.596</t>
+          <t>62595686.9896836</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.047</t>
+          <t>3046523.33684265</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.243</t>
+          <t>2243300.00000024</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.321</t>
+          <t>2321100.00000015</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2.313</t>
+          <t>2313199.99999966</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.249</t>
+          <t>2249099.99999999</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>2215099.99999973</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2.179</t>
+          <t>2178899.99999962</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.174</t>
+          <t>2173899.99999963</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.195</t>
+          <t>2195200.00000052</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2.249</t>
+          <t>2249300.0000005</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2.224</t>
+          <t>2223999.99999938</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2.292</t>
+          <t>2291899.99999956</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2.344</t>
+          <t>2344199.99999974</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.439</t>
+          <t>2439100.00000055</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2.382</t>
+          <t>2381599.9999996</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2360199.99999969</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2.311</t>
+          <t>2311199.99999988</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2.314</t>
+          <t>2313799.99999999</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2.319</t>
+          <t>2318999.99999986</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2.284</t>
+          <t>2284307.01725503</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2310113.8575942</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2.423</t>
+          <t>2423168.20029307</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2.353</t>
+          <t>2352595.53430261</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>2523370.75832088</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2.546</t>
+          <t>2545671.05272261</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2.621</t>
+          <t>2621150.55575794</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>2.769</t>
+          <t>2769242.27536417</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>1133556.67817282</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>909299.999999969</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>899799.999999948</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>920300.000000011</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>927200.000000258</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>912700.000000097</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>919100.000000021</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>935200.000000061</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>945999.999999943</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>920400.000000075</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.965</t>
+          <t>965499.999999995</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>973800.000000009</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>985900.000000113</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>1005900.00000013</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>991400.000000042</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>975099.999999875</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>962200.000000225</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>931500.000000102</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>918900.000000062</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>905652.792080042</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>889723.758863566</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>928335.306032193</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>919623.016102114</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>956117.545934962</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>1017403.4979944</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1055242.41956138</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1117459.36428547</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.995</t>
+          <t>3994661.9112242</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.203</t>
+          <t>4203199.99999982</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4.139</t>
+          <t>4138699.99999897</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4.063</t>
+          <t>4062800.00000029</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3.987</t>
+          <t>3986700.00000036</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.206</t>
+          <t>4205599.99999982</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.286</t>
+          <t>4285500.00000015</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4.492</t>
+          <t>4492300.0000007</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4.502</t>
+          <t>4502399.99999934</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4.505</t>
+          <t>4505000.00000065</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4.462</t>
+          <t>4461500.00000027</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4.478</t>
+          <t>4477599.99999931</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4.571</t>
+          <t>4571100.00000148</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4680400.00000058</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4.572</t>
+          <t>4572199.99999896</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>4.484</t>
+          <t>4483900.00000074</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>4.511</t>
+          <t>4511200.00000019</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4.604</t>
+          <t>4603699.99999996</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>4.631</t>
+          <t>4631299.99999913</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>4.624</t>
+          <t>4623718.11947782</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>4.378</t>
+          <t>4377689.38885488</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>4.404</t>
+          <t>4403962.09625447</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>4.254</t>
+          <t>4253550.56664217</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>4.242</t>
+          <t>4242281.58357038</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>4.213</t>
+          <t>4213429.92170953</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>4.154</t>
+          <t>4154396.96102212</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>3.954</t>
+          <t>3953649.35251211</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>28.658</t>
+          <t>28658365.5547437</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19.976</t>
+          <t>19975500.0000056</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20449699.9999942</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20.442</t>
+          <t>20442000.0000042</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20.952</t>
+          <t>20952399.9999994</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>21.477</t>
+          <t>21476600.0000028</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21639699.9999929</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>21.588</t>
+          <t>21588200.0000027</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>21.424</t>
+          <t>21423899.9999997</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>21.217</t>
+          <t>21216899.9999949</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>21.843</t>
+          <t>21842799.999999</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>22.322</t>
+          <t>22321799.9999986</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>20.488</t>
+          <t>20488299.9999997</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>20.815</t>
+          <t>20815299.999999</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>21.487</t>
+          <t>21487499.999999</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>21.265</t>
+          <t>21265199.9999989</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>22.589</t>
+          <t>22589099.9999976</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>24.094</t>
+          <t>24094200.0000033</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>24.814</t>
+          <t>24813999.9999987</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>25.172</t>
+          <t>25171897.9824138</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>23.919</t>
+          <t>23919351.6069653</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26.994</t>
+          <t>26994411.0440819</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>26.207</t>
+          <t>26207076.3045845</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>24.874</t>
+          <t>24874233.6202063</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>21.837</t>
+          <t>21836671.6669792</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22570412.674202</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>23.765</t>
+          <t>23765279.6275609</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>14.932</t>
+          <t>14931983.0752273</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.197</t>
+          <t>9196900.0000008</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>9.475</t>
+          <t>9474700.00000072</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>9.431</t>
+          <t>9431300.00000228</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>9.171</t>
+          <t>9170800.00000123</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8.684</t>
+          <t>8684199.99999927</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>9.203</t>
+          <t>9203299.99999823</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8.538</t>
+          <t>8538000.00000143</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8.907</t>
+          <t>8907300.00000028</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>9.463</t>
+          <t>9463000.00000034</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>9.672</t>
+          <t>9672099.9999999</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>9.619</t>
+          <t>9619199.99999904</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10110499.9999985</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>10.086</t>
+          <t>10086400.0000008</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>10.047</t>
+          <t>10046599.9999987</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>10.277</t>
+          <t>10276600.0000019</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>10.107</t>
+          <t>10106900.0000004</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>10.708</t>
+          <t>10708400.0000024</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>10.858</t>
+          <t>10857899.9999995</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>10.758</t>
+          <t>10757823.0398273</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>10.863</t>
+          <t>10863005.2571879</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>12.458</t>
+          <t>12457610.5109195</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>12.401</t>
+          <t>12400662.1132831</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13.345</t>
+          <t>13344669.6227304</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>13.402</t>
+          <t>13402075.1165835</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14.022</t>
+          <t>14022259.4396843</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>14.046</t>
+          <t>14046163.6413919</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>213.206</t>
+          <t>213205874.257203</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>128.167</t>
+          <t>128167499.999963</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>130.145</t>
+          <t>130145100.00001</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>118.832</t>
+          <t>118831700.000018</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>135.189</t>
+          <t>135189499.999978</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>137.353</t>
+          <t>137353100.000007</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>139.174</t>
+          <t>139174000.00003</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>139.22</t>
+          <t>139219999.999992</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>138.817</t>
+          <t>138816999.999978</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>123.654</t>
+          <t>123653999.999987</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>141.572</t>
+          <t>141572000.000006</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>127.07</t>
+          <t>127069999.999983</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>146.683</t>
+          <t>146683000.000022</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>148.29</t>
+          <t>148290000.000001</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>147.644</t>
+          <t>147644000.000035</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>142.184</t>
+          <t>142184000.000006</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>141.382</t>
+          <t>141382000.000035</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>122.895</t>
+          <t>122894999.999995</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>144.753</t>
+          <t>144752999.999993</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>141.957</t>
+          <t>141957010.986604</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>146.066</t>
+          <t>146065526.662999</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>185.031</t>
+          <t>185030568.825713</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>185.632</t>
+          <t>185632324.561415</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>191.95</t>
+          <t>191950288.082137</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>186.49</t>
+          <t>186489822.873518</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>209.304</t>
+          <t>209303585.57967</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>211.026</t>
+          <t>211026379.468675</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5030.831</t>
+          <t>5030830622.12558</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2421.185</t>
+          <t>2421184553.00005</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2460.121</t>
+          <t>2460120922.00008</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2481.973</t>
+          <t>2481972520.00021</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2525.223</t>
+          <t>2525222686.00019</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2569.599</t>
+          <t>2569599396.99984</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2602.571</t>
+          <t>2602571446.00022</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2643.028</t>
+          <t>2643028113</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2683.428</t>
+          <t>2683428103.99983</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2709.457</t>
+          <t>2709457044.00017</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2765.362</t>
+          <t>2765362170.99963</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2796.728</t>
+          <t>2796728309.99991</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2862.592</t>
+          <t>2862591956.99984</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2945.443</t>
+          <t>2945442663.00011</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2944.472</t>
+          <t>2944472079.00002</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2965.027</t>
+          <t>2965027470.00019</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>3024.664</t>
+          <t>3024664026.00034</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>3042.368</t>
+          <t>3042368246.99991</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>3104.553</t>
+          <t>3104552511.99989</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>3114.106</t>
+          <t>3114105934.70157</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>3152.194</t>
+          <t>3152193813.76175</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>3546.102</t>
+          <t>3546101709.8212</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>3531.887</t>
+          <t>3531887168.07331</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3730.031</t>
+          <t>3730031407.21429</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>3746.113</t>
+          <t>3746112812.75699</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>4065.732</t>
+          <t>4065731583.40256</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4221.8</t>
+          <t>4221800255.62903</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.824</t>
+          <t>1824001.26903438</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1547700.00000019</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1556599.99999999</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1566099.99999958</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>1600799.99999983</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.508</t>
+          <t>1508199.99999985</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>1611000.00000009</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1524900.00000009</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1559099.99999972</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1588100.0000004</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1638299.99999987</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1629499.99999984</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1.634</t>
+          <t>1633500</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1.673</t>
+          <t>1672899.99999969</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.634</t>
+          <t>1633800.00000017</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1604700.00000026</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1539699.99999985</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1490899.99999977</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1443500.00000031</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1447922.22996223</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1435433.25183425</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1431958.48937089</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1527869.10698391</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1519551.1984175</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1629152.8963939</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>1.656</t>
+          <t>1656370.06001228</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1.731</t>
+          <t>1730920.41056508</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4.371</t>
+          <t>4371382.43163532</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>3675099.99999876</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3.272</t>
+          <t>3272399.99999889</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3.639</t>
+          <t>3638899.99999968</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.677</t>
+          <t>3676899.99999919</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3309900.00000032</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3.302</t>
+          <t>3302399.99999875</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3.475</t>
+          <t>3475099.99999956</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>3.464</t>
+          <t>3464200.00000002</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3.938</t>
+          <t>3937699.99999896</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3.459</t>
+          <t>3458599.99999917</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>3.467</t>
+          <t>3466700.00000005</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>3.528</t>
+          <t>3527800.00000076</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4079599.99999953</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>3.414</t>
+          <t>3414100.00000034</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>4.031</t>
+          <t>4030799.99999948</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3550399.99999961</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>4.172</t>
+          <t>4171700.00000046</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>4.239</t>
+          <t>4239000.00000075</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>4.265</t>
+          <t>4265337.02471793</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>4.101</t>
+          <t>4100857.95687958</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>4.528</t>
+          <t>4527609.40538153</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>4.517</t>
+          <t>4517146.45372896</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>4.332</t>
+          <t>4331756.26377686</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>4.185</t>
+          <t>4184732.12345744</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>4.428</t>
+          <t>4428320.14651819</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>4.311</t>
+          <t>4310577.90265604</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2.354</t>
+          <t>2354440.90947713</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.135</t>
+          <t>2135000.00000031</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2.204</t>
+          <t>2203999.99999991</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.263</t>
+          <t>2263000.00000004</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.332</t>
+          <t>2332100.00000035</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.348</t>
+          <t>2347799.99999971</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.364</t>
+          <t>2364399.99999936</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2.372</t>
+          <t>2372099.99999966</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.379</t>
+          <t>2379199.99999979</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2.345</t>
+          <t>2344900.00000062</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2.355</t>
+          <t>2355299.99999999</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2.366</t>
+          <t>2366200.00000065</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2440000.00000051</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2.522</t>
+          <t>2521500.00000044</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2.447</t>
+          <t>2447200.00000019</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2.498</t>
+          <t>2497799.99999954</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2.499</t>
+          <t>2499000.00000014</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2.533</t>
+          <t>2532800.00000029</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2.581</t>
+          <t>2580999.99999971</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2.562</t>
+          <t>2562074.01266265</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>2.433</t>
+          <t>2433107.87443401</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>2250755.32954556</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2.171</t>
+          <t>2170537.86370219</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2.186</t>
+          <t>2185964.50090536</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2.121</t>
+          <t>2121311.26005411</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2.155</t>
+          <t>2155379.76837386</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>2.316</t>
+          <t>2315709.61387955</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>15.167</t>
+          <t>15167263.775819</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13.026</t>
+          <t>13026399.9999975</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13.272</t>
+          <t>13271700.0000054</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>13.128</t>
+          <t>13127600.0000008</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>12.751</t>
+          <t>12750700</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>12.532</t>
+          <t>12531500.0000004</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11.444</t>
+          <t>11443899.9999982</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>11.138</t>
+          <t>11137900.000002</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>11.225</t>
+          <t>11224900</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>11.388</t>
+          <t>11388100</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>11.617</t>
+          <t>11617000.0000011</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>12.272</t>
+          <t>12272100.0000002</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>12.768</t>
+          <t>12767899.9999981</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>13.184</t>
+          <t>13184000.0000007</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>13709999.9999982</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>13.303</t>
+          <t>13303099.9999981</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>13.253</t>
+          <t>13252600.0000006</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13.202</t>
+          <t>13202399.9999997</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>13.475</t>
+          <t>13475199.9999982</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>11.648</t>
+          <t>11648270.7163993</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>11.297</t>
+          <t>11297169.886747</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>12.588</t>
+          <t>12588177.8159103</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>11.814</t>
+          <t>11813924.7561265</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12.881</t>
+          <t>12880888.8851043</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>13230116.9201489</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13.319</t>
+          <t>13319384.8630318</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>13.424</t>
+          <t>13424116.1566441</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>768.486</t>
+          <t>768485610.167921</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>304.7</t>
+          <t>304700000.000037</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>311.522</t>
+          <t>311521999.999862</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>320.948</t>
+          <t>320948000.000028</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>366.697</t>
+          <t>366696999.999955</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>367.642</t>
+          <t>367641999.999972</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>375.327</t>
+          <t>375327000.000154</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>392.807</t>
+          <t>392806999.999977</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>416.161</t>
+          <t>416160999.999947</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>444.073</t>
+          <t>444073000.000019</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>461.459</t>
+          <t>461459000.000023</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>466.145</t>
+          <t>466145000.000049</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>467.728</t>
+          <t>467727999.999993</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>495.106</t>
+          <t>495105999.999956</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>497.754</t>
+          <t>497754000.000033</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>533.626</t>
+          <t>533626000.000076</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>532.475</t>
+          <t>532475000.000162</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>528.534</t>
+          <t>528534000.000061</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>528.691</t>
+          <t>528691000.00001</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>522.242</t>
+          <t>522242446.306617</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>512.582</t>
+          <t>512581915.295473</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>561.923</t>
+          <t>561923016.966606</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>555.926</t>
+          <t>555926114.69131</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>574.311</t>
+          <t>574310884.760153</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>564.709</t>
+          <t>564709002.786384</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>603.868</t>
+          <t>603868109.258634</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>627.844</t>
+          <t>627844181.931736</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>122.06</t>
+          <t>122059963.744534</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>87.049</t>
+          <t>87049000.0000008</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>90.78</t>
+          <t>90779999.9999937</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>90.656</t>
+          <t>90655999.9999751</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>92.383</t>
+          <t>92383000.0000113</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>93.349</t>
+          <t>93349000.0000037</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>94.359</t>
+          <t>94359000.0000313</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.827</t>
+          <t>96826999.9999953</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>99.675</t>
+          <t>99675000.0000131</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>102.991</t>
+          <t>102991000.000009</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>102.085</t>
+          <t>102085000.000004</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>104.141</t>
+          <t>104140999.99998</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>105.491</t>
+          <t>105490999.999979</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>112.925</t>
+          <t>112924999.999989</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>114.717</t>
+          <t>114717000.000015</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>116.412</t>
+          <t>116411999.999984</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>122.3</t>
+          <t>122299999.999994</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>125.737</t>
+          <t>125736999.999992</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>125.412</t>
+          <t>125412000.000002</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>122.161</t>
+          <t>122161057.782419</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>118.586</t>
+          <t>118586208.193096</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>136.786</t>
+          <t>136785613.475145</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>123.636</t>
+          <t>123636335.768257</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128199948.004368</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>114.855</t>
+          <t>114855316.264331</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>112.705</t>
+          <t>112705464.675208</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>111.008</t>
+          <t>111008291.495691</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>211.852</t>
+          <t>211852352.51986</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>149.957</t>
+          <t>149957000.000006</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>149.48</t>
+          <t>149480000.000008</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>149.337</t>
+          <t>149337000.000009</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>148.994</t>
+          <t>148993999.999996</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>148.838</t>
+          <t>148838000.000028</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147900000.000017</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>149.251</t>
+          <t>149251000.000044</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>150.6</t>
+          <t>150600000.000045</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>151.951</t>
+          <t>151950999.999985</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>153.3</t>
+          <t>153300000.000007</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>154.651</t>
+          <t>154651000.000022</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>156000000.000032</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>158.7</t>
+          <t>158700000.000034</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>159.3</t>
+          <t>159299999.999995</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>159.9</t>
+          <t>159900000.000011</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>161.1</t>
+          <t>161099999.999974</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>163.9</t>
+          <t>163899999.999993</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>163.562</t>
+          <t>163562000.000001</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>167.823</t>
+          <t>167823121.288206</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>143.396</t>
+          <t>143395651.777559</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>133.292</t>
+          <t>133292244.241328</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>132.866</t>
+          <t>132865838.800824</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>147.461</t>
+          <t>147460546.739119</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>159.184</t>
+          <t>159184163.488529</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>178.044</t>
+          <t>178043663.991897</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>183.386</t>
+          <t>183386119.448844</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>509.606</t>
+          <t>509605962.530908</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>226.434</t>
+          <t>226434000.000006</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>232.371</t>
+          <t>232371000.000035</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>238.824</t>
+          <t>238824000.000065</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>245.646</t>
+          <t>245646000.00003</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>252.473</t>
+          <t>252472999.999921</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>259.664</t>
+          <t>259664000.000049</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>268.625</t>
+          <t>268625000</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>276.5</t>
+          <t>276499999.99999</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>284.3</t>
+          <t>284299999.999967</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>292.033</t>
+          <t>292032999.999986</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>299.341</t>
+          <t>299340999.99993</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>306.807</t>
+          <t>306806999.99992</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>322.316</t>
+          <t>322316000.000072</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>328.615</t>
+          <t>328614999.999911</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>335.848</t>
+          <t>335847999.99998</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>349.548</t>
+          <t>349548000.00002</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>359.598</t>
+          <t>359597999.999865</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>368.903</t>
+          <t>368902999.99998</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>385.541</t>
+          <t>385540972.611035</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>392.786</t>
+          <t>392785805.810605</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>423.836</t>
+          <t>423835505.57822</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>406.319</t>
+          <t>406318999.080115</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>409.76</t>
+          <t>409760044.778252</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>412.145</t>
+          <t>412145311.10041</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>452.678</t>
+          <t>452678269.077915</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>464.149</t>
+          <t>464148798.826713</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>44740182.2627692</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19.412</t>
+          <t>19412199.9999909</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.676</t>
+          <t>19676299.9999981</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20429999.9999986</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20.668</t>
+          <t>20668200.0000029</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>20.902</t>
+          <t>20901599.9999948</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19460300.0000056</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>21.312</t>
+          <t>21311800.0000055</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>23.276</t>
+          <t>23276100.0000046</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>25.283</t>
+          <t>25283100.0000006</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>26.457</t>
+          <t>26457200.0000033</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>27.778</t>
+          <t>27778200.000002</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>31.412</t>
+          <t>31411699.9999962</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>34.685</t>
+          <t>34684700.0000032</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>35.388</t>
+          <t>35387500.0000128</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>36.985</t>
+          <t>36984799.9999911</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>38.411</t>
+          <t>38410900.0000081</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>38.706</t>
+          <t>38705799.9999978</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>39170000.0000051</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>36800172.5746044</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>34.862</t>
+          <t>34861932.4069963</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>38.19</t>
+          <t>38189616.0760536</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>37.361</t>
+          <t>37360628.5767495</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>37.248</t>
+          <t>37248094.2997875</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>37.591</t>
+          <t>37591491.7470502</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>41.006</t>
+          <t>41005610.5684441</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>42.729</t>
+          <t>42729332.0311593</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8067,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
